--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/08 Agosto/Liquidacióncvs -agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4394" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3674B598-C471-44DF-8D42-798F34AC27B1}"/>
+  <xr:revisionPtr revIDLastSave="4412" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{068EF6FE-60C7-4F83-AC39-C8132CF3992C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja2" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$6886</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$6890</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11420" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11432" uniqueCount="102">
   <si>
     <t>Sucursal</t>
   </si>
@@ -721,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}">
-  <dimension ref="A1:H7121"/>
+  <dimension ref="A1:H7125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -73000,10 +73000,10 @@
     </row>
     <row r="2801" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2801" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2801" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="F2801" t="s">
         <v>65</v>
@@ -73014,13 +73014,13 @@
     </row>
     <row r="2802" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2802" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B2802" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="F2802" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G2802">
         <v>0</v>
@@ -73031,7 +73031,7 @@
         <v>46239</v>
       </c>
       <c r="B2803" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F2803" t="s">
         <v>80</v>
@@ -73042,10 +73042,10 @@
     </row>
     <row r="2804" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2804" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B2804" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F2804" t="s">
         <v>80</v>
@@ -73059,7 +73059,7 @@
         <v>46239</v>
       </c>
       <c r="B2805" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2805" t="s">
         <v>80</v>
@@ -73070,10 +73070,10 @@
     </row>
     <row r="2806" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2806" s="2">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="B2806" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F2806" t="s">
         <v>80</v>
@@ -73087,7 +73087,7 @@
         <v>46239</v>
       </c>
       <c r="B2807" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F2807" t="s">
         <v>80</v>
@@ -73098,10 +73098,10 @@
     </row>
     <row r="2808" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2808" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B2808" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F2808" t="s">
         <v>80</v>
@@ -73112,10 +73112,10 @@
     </row>
     <row r="2809" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2809" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2809" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F2809" t="s">
         <v>80</v>
@@ -73126,10 +73126,10 @@
     </row>
     <row r="2810" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2810" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B2810" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F2810" t="s">
         <v>80</v>
@@ -73143,7 +73143,7 @@
         <v>46240</v>
       </c>
       <c r="B2811" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2811" t="s">
         <v>80</v>
@@ -73154,10 +73154,10 @@
     </row>
     <row r="2812" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2812" s="2">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B2812" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F2812" t="s">
         <v>80</v>
@@ -73168,10 +73168,10 @@
     </row>
     <row r="2813" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2813" s="2">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B2813" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F2813" t="s">
         <v>80</v>
@@ -73182,10 +73182,10 @@
     </row>
     <row r="2814" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2814" s="2">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B2814" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F2814" t="s">
         <v>80</v>
@@ -73196,10 +73196,10 @@
     </row>
     <row r="2815" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2815" s="2">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="B2815" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F2815" t="s">
         <v>80</v>
@@ -73210,10 +73210,10 @@
     </row>
     <row r="2816" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2816" s="2">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="B2816" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F2816" t="s">
         <v>80</v>
@@ -73227,7 +73227,7 @@
         <v>46237</v>
       </c>
       <c r="B2817" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="F2817" t="s">
         <v>80</v>
@@ -73238,10 +73238,10 @@
     </row>
     <row r="2818" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2818" s="2">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="B2818" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F2818" t="s">
         <v>80</v>
@@ -73252,10 +73252,10 @@
     </row>
     <row r="2819" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2819" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B2819" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F2819" t="s">
         <v>80</v>
@@ -73266,10 +73266,10 @@
     </row>
     <row r="2820" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2820" s="2">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="B2820" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F2820" t="s">
         <v>80</v>
@@ -73280,10 +73280,10 @@
     </row>
     <row r="2821" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2821" s="2">
-        <v>46240</v>
+        <v>46235</v>
       </c>
       <c r="B2821" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F2821" t="s">
         <v>80</v>
@@ -73294,10 +73294,10 @@
     </row>
     <row r="2822" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2822" s="2">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="B2822" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F2822" t="s">
         <v>80</v>
@@ -73308,10 +73308,10 @@
     </row>
     <row r="2823" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2823" s="2">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B2823" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2823" t="s">
         <v>80</v>
@@ -73322,10 +73322,10 @@
     </row>
     <row r="2824" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2824" s="2">
-        <v>46240</v>
+        <v>46235</v>
       </c>
       <c r="B2824" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="F2824" t="s">
         <v>80</v>
@@ -73336,10 +73336,10 @@
     </row>
     <row r="2825" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2825" s="2">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="B2825" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="F2825" t="s">
         <v>80</v>
@@ -73350,10 +73350,10 @@
     </row>
     <row r="2826" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2826" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B2826" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F2826" t="s">
         <v>80</v>
@@ -73364,22 +73364,13 @@
     </row>
     <row r="2827" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2827" s="2">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B2827" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2827">
-        <v>43629101</v>
-      </c>
-      <c r="D2827" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2827" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F2827" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2827">
         <v>0</v>
@@ -73387,22 +73378,13 @@
     </row>
     <row r="2828" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2828" s="2">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="B2828" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2828">
-        <v>43262406</v>
-      </c>
-      <c r="D2828" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2828" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F2828" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G2828">
         <v>0</v>
@@ -73410,16 +73392,16 @@
     </row>
     <row r="2829" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2829" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B2829" t="s">
         <v>12</v>
       </c>
       <c r="C2829">
-        <v>1039679117</v>
+        <v>43629101</v>
       </c>
       <c r="D2829" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="E2829" t="s">
         <v>50</v>
@@ -73433,16 +73415,16 @@
     </row>
     <row r="2830" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2830" s="2">
-        <v>46238</v>
+        <v>46249</v>
       </c>
       <c r="B2830" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="C2830">
-        <v>1020401814</v>
+        <v>1042060895</v>
       </c>
       <c r="D2830" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="E2830" t="s">
         <v>50</v>
@@ -73456,19 +73438,19 @@
     </row>
     <row r="2831" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2831" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B2831" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="C2831">
-        <v>1017283114</v>
+        <v>10394519000</v>
       </c>
       <c r="D2831" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E2831" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2831" t="s">
         <v>91</v>
@@ -73479,16 +73461,16 @@
     </row>
     <row r="2832" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2832" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2832" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C2832">
-        <v>1000922411</v>
+        <v>43262406</v>
       </c>
       <c r="D2832" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E2832" t="s">
         <v>50</v>
@@ -73505,13 +73487,13 @@
         <v>46239</v>
       </c>
       <c r="B2833" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C2833">
-        <v>1007471096</v>
+        <v>1039679117</v>
       </c>
       <c r="D2833" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E2833" t="s">
         <v>50</v>
@@ -73525,19 +73507,19 @@
     </row>
     <row r="2834" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2834" s="2">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B2834" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C2834">
-        <v>1040511721</v>
+        <v>1020401814</v>
       </c>
       <c r="D2834" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E2834" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2834" t="s">
         <v>91</v>
@@ -73548,16 +73530,16 @@
     </row>
     <row r="2835" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2835" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2835" t="s">
         <v>32</v>
       </c>
       <c r="C2835">
-        <v>1017160164</v>
+        <v>1017283114</v>
       </c>
       <c r="D2835" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E2835" t="s">
         <v>50</v>
@@ -73571,16 +73553,16 @@
     </row>
     <row r="2836" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2836" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B2836" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C2836">
-        <v>1036689035</v>
+        <v>1000922411</v>
       </c>
       <c r="D2836" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E2836" t="s">
         <v>50</v>
@@ -73594,16 +73576,16 @@
     </row>
     <row r="2837" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2837" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2837" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2837">
-        <v>10016196451</v>
+        <v>1007471096</v>
       </c>
       <c r="D2837" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E2837" t="s">
         <v>50</v>
@@ -73617,19 +73599,19 @@
     </row>
     <row r="2838" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2838" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2838" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C2838">
-        <v>1017284920</v>
+        <v>1040511721</v>
       </c>
       <c r="D2838" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="E2838" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2838" t="s">
         <v>91</v>
@@ -73640,16 +73622,16 @@
     </row>
     <row r="2839" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2839" s="2">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B2839" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C2839">
-        <v>1037548867</v>
+        <v>1017160164</v>
       </c>
       <c r="D2839" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E2839" t="s">
         <v>50</v>
@@ -73663,16 +73645,16 @@
     </row>
     <row r="2840" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2840" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B2840" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C2840">
-        <v>1037603803</v>
+        <v>1036689035</v>
       </c>
       <c r="D2840" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E2840" t="s">
         <v>50</v>
@@ -73686,16 +73668,16 @@
     </row>
     <row r="2841" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2841" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B2841" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C2841">
-        <v>1026145688</v>
+        <v>10016196451</v>
       </c>
       <c r="D2841" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="E2841" t="s">
         <v>50</v>
@@ -73709,16 +73691,16 @@
     </row>
     <row r="2842" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2842" s="2">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B2842" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C2842">
-        <v>1060593889</v>
+        <v>1017284920</v>
       </c>
       <c r="D2842" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E2842" t="s">
         <v>50</v>
@@ -73732,16 +73714,16 @@
     </row>
     <row r="2843" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2843" s="2">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="B2843" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C2843">
-        <v>1060593889</v>
+        <v>1037548867</v>
       </c>
       <c r="D2843" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2843" t="s">
         <v>50</v>
@@ -73758,13 +73740,13 @@
         <v>46235</v>
       </c>
       <c r="B2844" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C2844">
-        <v>1060593889</v>
+        <v>1037603803</v>
       </c>
       <c r="D2844" t="s">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="E2844" t="s">
         <v>50</v>
@@ -73778,19 +73760,19 @@
     </row>
     <row r="2845" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2845" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B2845" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C2845">
-        <v>431140540</v>
+        <v>1026145688</v>
       </c>
       <c r="D2845" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="E2845" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2845" t="s">
         <v>91</v>
@@ -73804,16 +73786,16 @@
         <v>46238</v>
       </c>
       <c r="B2846" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C2846">
-        <v>432553771</v>
+        <v>1060593889</v>
       </c>
       <c r="D2846" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E2846" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2846" t="s">
         <v>91</v>
@@ -73824,16 +73806,16 @@
     </row>
     <row r="2847" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2847" s="2">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B2847" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C2847">
-        <v>1042774546</v>
+        <v>1060593889</v>
       </c>
       <c r="D2847" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2847" t="s">
         <v>50</v>
@@ -73850,13 +73832,13 @@
         <v>46235</v>
       </c>
       <c r="B2848" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2848">
-        <v>1001547741</v>
+        <v>1060593889</v>
       </c>
       <c r="D2848" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="E2848" t="s">
         <v>50</v>
@@ -73873,16 +73855,16 @@
         <v>46235</v>
       </c>
       <c r="B2849" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C2849">
-        <v>1039596837</v>
+        <v>431140540</v>
       </c>
       <c r="D2849" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E2849" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2849" t="s">
         <v>91</v>
@@ -73893,16 +73875,16 @@
     </row>
     <row r="2850" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2850" s="2">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="B2850" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C2850">
-        <v>31274520</v>
+        <v>432553771</v>
       </c>
       <c r="D2850" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E2850" t="s">
         <v>49</v>
@@ -73916,19 +73898,19 @@
     </row>
     <row r="2851" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2851" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B2851" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C2851">
-        <v>10392893281</v>
+        <v>1042774546</v>
       </c>
       <c r="D2851" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2851" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2851" t="s">
         <v>91</v>
@@ -73939,19 +73921,19 @@
     </row>
     <row r="2852" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2852" s="2">
-        <v>46240</v>
+        <v>46235</v>
       </c>
       <c r="B2852" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C2852">
-        <v>10375445591</v>
+        <v>1001547741</v>
       </c>
       <c r="D2852" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E2852" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2852" t="s">
         <v>91</v>
@@ -73962,19 +73944,19 @@
     </row>
     <row r="2853" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2853" s="2">
-        <v>46239</v>
+        <v>46235</v>
       </c>
       <c r="B2853" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C2853">
-        <v>10383384661</v>
+        <v>1039596837</v>
       </c>
       <c r="D2853" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E2853" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2853" t="s">
         <v>91</v>
@@ -73985,16 +73967,16 @@
     </row>
     <row r="2854" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2854" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B2854" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C2854">
-        <v>10427737531</v>
+        <v>31274520</v>
       </c>
       <c r="D2854" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E2854" t="s">
         <v>49</v>
@@ -74008,16 +73990,16 @@
     </row>
     <row r="2855" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2855" s="2">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B2855" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C2855">
-        <v>10334271340</v>
+        <v>10392893281</v>
       </c>
       <c r="D2855" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="E2855" t="s">
         <v>49</v>
@@ -74031,16 +74013,16 @@
     </row>
     <row r="2856" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2856" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B2856" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C2856">
-        <v>10172503533</v>
+        <v>10375445591</v>
       </c>
       <c r="D2856" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="E2856" t="s">
         <v>49</v>
@@ -74054,16 +74036,16 @@
     </row>
     <row r="2857" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2857" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2857" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C2857">
-        <v>10171674991</v>
+        <v>10383384661</v>
       </c>
       <c r="D2857" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E2857" t="s">
         <v>49</v>
@@ -74080,13 +74062,13 @@
         <v>46239</v>
       </c>
       <c r="B2858" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C2858">
-        <v>432786341</v>
+        <v>10427737531</v>
       </c>
       <c r="D2858" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="E2858" t="s">
         <v>49</v>
@@ -74100,16 +74082,16 @@
     </row>
     <row r="2859" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2859" s="2">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B2859" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C2859">
-        <v>11284350761</v>
+        <v>10334271340</v>
       </c>
       <c r="D2859" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E2859" t="s">
         <v>49</v>
@@ -74123,16 +74105,16 @@
     </row>
     <row r="2860" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2860" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2860" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2860">
-        <v>11284755861</v>
+        <v>10172503533</v>
       </c>
       <c r="D2860" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2860" t="s">
         <v>49</v>
@@ -74146,16 +74128,16 @@
     </row>
     <row r="2861" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2861" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B2861" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C2861">
-        <v>10336528361</v>
+        <v>10171674991</v>
       </c>
       <c r="D2861" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E2861" t="s">
         <v>49</v>
@@ -74169,16 +74151,16 @@
     </row>
     <row r="2862" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2862" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2862" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C2862">
-        <v>10386260211</v>
+        <v>432786341</v>
       </c>
       <c r="D2862" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E2862" t="s">
         <v>49</v>
@@ -74192,16 +74174,16 @@
     </row>
     <row r="2863" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2863" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B2863" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C2863">
-        <v>11284649230</v>
+        <v>11284350761</v>
       </c>
       <c r="D2863" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="E2863" t="s">
         <v>49</v>
@@ -74215,16 +74197,16 @@
     </row>
     <row r="2864" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2864" s="2">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B2864" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C2864">
-        <v>438075071</v>
+        <v>11284755861</v>
       </c>
       <c r="D2864" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="E2864" t="s">
         <v>49</v>
@@ -74238,19 +74220,19 @@
     </row>
     <row r="2865" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2865" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B2865" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C2865">
-        <v>1067097487</v>
+        <v>10336528361</v>
       </c>
       <c r="D2865" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E2865" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2865" t="s">
         <v>91</v>
@@ -74261,19 +74243,19 @@
     </row>
     <row r="2866" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2866" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B2866" t="s">
         <v>25</v>
       </c>
       <c r="C2866">
-        <v>1128483659</v>
+        <v>10386260211</v>
       </c>
       <c r="D2866" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E2866" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2866" t="s">
         <v>91</v>
@@ -74284,19 +74266,19 @@
     </row>
     <row r="2867" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2867" s="2">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B2867" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C2867">
-        <v>1032011765</v>
+        <v>11284649230</v>
       </c>
       <c r="D2867" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E2867" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2867" t="s">
         <v>91</v>
@@ -74307,19 +74289,19 @@
     </row>
     <row r="2868" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2868" s="2">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="B2868" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C2868">
-        <v>1192897</v>
+        <v>438075071</v>
       </c>
       <c r="D2868" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2868" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2868" t="s">
         <v>91</v>
@@ -74333,13 +74315,13 @@
         <v>46235</v>
       </c>
       <c r="B2869" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C2869">
-        <v>1233344333</v>
+        <v>1067097487</v>
       </c>
       <c r="D2869" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="E2869" t="s">
         <v>50</v>
@@ -74353,19 +74335,19 @@
     </row>
     <row r="2870" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2870" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B2870" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C2870">
-        <v>1038135458</v>
+        <v>1128483659</v>
       </c>
       <c r="D2870" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E2870" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2870" t="s">
         <v>91</v>
@@ -74379,13 +74361,13 @@
         <v>46238</v>
       </c>
       <c r="B2871" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2871">
-        <v>43264120</v>
+        <v>1032011765</v>
       </c>
       <c r="D2871" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E2871" t="s">
         <v>50</v>
@@ -74399,16 +74381,16 @@
     </row>
     <row r="2872" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2872" s="2">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B2872" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C2872">
-        <v>1000444316</v>
+        <v>1192897</v>
       </c>
       <c r="D2872" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="E2872" t="s">
         <v>50</v>
@@ -74425,16 +74407,16 @@
         <v>46235</v>
       </c>
       <c r="B2873" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C2873">
-        <v>1000444316</v>
+        <v>1233344333</v>
       </c>
       <c r="D2873" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="E2873" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2873" t="s">
         <v>91</v>
@@ -74448,16 +74430,16 @@
         <v>46235</v>
       </c>
       <c r="B2874" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C2874">
-        <v>1035227857</v>
+        <v>1038135458</v>
       </c>
       <c r="D2874" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="E2874" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2874" t="s">
         <v>91</v>
@@ -74468,19 +74450,19 @@
     </row>
     <row r="2875" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2875" s="2">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="B2875" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C2875">
-        <v>1038137799</v>
+        <v>43264120</v>
       </c>
       <c r="D2875" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="E2875" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2875" t="s">
         <v>91</v>
@@ -74491,16 +74473,16 @@
     </row>
     <row r="2876" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2876" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B2876" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C2876">
-        <v>1002148260</v>
+        <v>1000444316</v>
       </c>
       <c r="D2876" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E2876" t="s">
         <v>50</v>
@@ -74514,19 +74496,19 @@
     </row>
     <row r="2877" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2877" s="2">
-        <v>46240</v>
+        <v>46235</v>
       </c>
       <c r="B2877" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C2877">
-        <v>1039597884</v>
+        <v>1000444316</v>
       </c>
       <c r="D2877" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="E2877" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2877" t="s">
         <v>91</v>
@@ -74537,22 +74519,22 @@
     </row>
     <row r="2878" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2878" s="2">
-        <v>46240</v>
+        <v>46235</v>
       </c>
       <c r="B2878" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C2878">
-        <v>10384803501</v>
+        <v>1035227857</v>
       </c>
       <c r="D2878" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="E2878" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2878" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="G2878">
         <v>0</v>
@@ -74563,39 +74545,115 @@
         <v>46240</v>
       </c>
       <c r="B2879" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="C2879">
-        <v>10394519000</v>
+        <v>1038137799</v>
       </c>
       <c r="D2879" t="s">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="E2879" t="s">
         <v>49</v>
       </c>
       <c r="F2879" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="G2879">
         <v>0</v>
       </c>
     </row>
     <row r="2880" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2880" s="2"/>
-      <c r="G2880"/>
+      <c r="A2880" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B2880" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2880">
+        <v>1002148260</v>
+      </c>
+      <c r="D2880" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2880" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2880" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2880">
+        <v>0</v>
+      </c>
     </row>
     <row r="2881" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2881" s="2"/>
-      <c r="G2881"/>
+      <c r="A2881" s="2">
+        <v>46240</v>
+      </c>
+      <c r="B2881" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2881">
+        <v>1039597884</v>
+      </c>
+      <c r="D2881" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2881" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2881" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2881">
+        <v>0</v>
+      </c>
     </row>
     <row r="2882" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2882" s="2"/>
-      <c r="G2882"/>
+      <c r="A2882" s="2">
+        <v>46240</v>
+      </c>
+      <c r="B2882" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2882">
+        <v>10384803501</v>
+      </c>
+      <c r="D2882" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2882" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2882" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2882">
+        <v>0</v>
+      </c>
     </row>
     <row r="2883" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2883" s="2"/>
-      <c r="G2883"/>
+      <c r="A2883" s="2">
+        <v>46240</v>
+      </c>
+      <c r="B2883" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2883">
+        <v>10394519000</v>
+      </c>
+      <c r="D2883" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2883" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2883" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2883">
+        <v>0</v>
+      </c>
     </row>
     <row r="2884" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2884" s="2"/>
@@ -90391,113 +90449,113 @@
     </row>
     <row r="6832" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6832" s="2"/>
-      <c r="F6832" s="3"/>
-    </row>
-    <row r="6833" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6832"/>
+    </row>
+    <row r="6833" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6833" s="2"/>
-      <c r="F6833" s="3"/>
-    </row>
-    <row r="6834" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6833"/>
+    </row>
+    <row r="6834" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6834" s="2"/>
-      <c r="F6834" s="3"/>
-    </row>
-    <row r="6835" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6834"/>
+    </row>
+    <row r="6835" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6835" s="2"/>
-      <c r="F6835" s="3"/>
-    </row>
-    <row r="6836" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6835"/>
+    </row>
+    <row r="6836" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6836" s="2"/>
-    </row>
-    <row r="6837" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6836" s="3"/>
+    </row>
+    <row r="6837" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6837" s="2"/>
-    </row>
-    <row r="6838" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6837" s="3"/>
+    </row>
+    <row r="6838" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6838" s="2"/>
-    </row>
-    <row r="6839" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6838" s="3"/>
+    </row>
+    <row r="6839" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6839" s="2"/>
-    </row>
-    <row r="6840" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6839" s="3"/>
+    </row>
+    <row r="6840" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6840" s="2"/>
     </row>
-    <row r="6841" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6841" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6841" s="2"/>
     </row>
-    <row r="6842" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6842" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6842" s="2"/>
     </row>
-    <row r="6843" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6843" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6843" s="2"/>
     </row>
-    <row r="6844" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6844" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6844" s="2"/>
     </row>
-    <row r="6845" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6845" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6845" s="2"/>
     </row>
-    <row r="6846" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6846" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6846" s="2"/>
     </row>
-    <row r="6847" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6847" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6847" s="2"/>
     </row>
-    <row r="6848" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6848" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6848" s="2"/>
     </row>
-    <row r="6849" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6849" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6849" s="2"/>
     </row>
-    <row r="6850" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6850" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6850" s="2"/>
     </row>
-    <row r="6851" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6851" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6851" s="2"/>
     </row>
-    <row r="6852" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6852" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6852" s="2"/>
     </row>
-    <row r="6853" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6853" s="2"/>
     </row>
-    <row r="6854" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6854" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6854" s="2"/>
     </row>
-    <row r="6855" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6855" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6855" s="2"/>
     </row>
-    <row r="6856" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6856" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6856" s="2"/>
     </row>
-    <row r="6857" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6857" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6857" s="2"/>
     </row>
-    <row r="6858" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6858" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6858" s="2"/>
     </row>
-    <row r="6859" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6859" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6859" s="2"/>
     </row>
-    <row r="6860" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6860" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6860" s="2"/>
     </row>
-    <row r="6861" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6861" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6861" s="2"/>
     </row>
-    <row r="6862" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6862" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6862" s="2"/>
-      <c r="G6862"/>
-    </row>
-    <row r="6863" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6863" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6863" s="2"/>
-      <c r="G6863"/>
-    </row>
-    <row r="6864" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6864" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6864" s="2"/>
-      <c r="G6864"/>
     </row>
     <row r="6865" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6865" s="2"/>
-      <c r="G6865"/>
     </row>
     <row r="6866" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6866" s="2"/>
@@ -90585,15 +90643,19 @@
     </row>
     <row r="6887" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6887" s="2"/>
+      <c r="G6887"/>
     </row>
     <row r="6888" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6888" s="2"/>
+      <c r="G6888"/>
     </row>
     <row r="6889" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6889" s="2"/>
+      <c r="G6889"/>
     </row>
     <row r="6890" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6890" s="2"/>
+      <c r="G6890"/>
     </row>
     <row r="6891" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6891" s="2"/>
@@ -91288,8 +91350,20 @@
     <row r="7121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7121" s="2"/>
     </row>
+    <row r="7122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7122" s="2"/>
+    </row>
+    <row r="7123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7123" s="2"/>
+    </row>
+    <row r="7124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7124" s="2"/>
+    </row>
+    <row r="7125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7125" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H6886" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}"/>
+  <autoFilter ref="A1:H6890" xr:uid="{14AE435F-C8B7-4B0C-8617-5994DE6D3EA0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/08 Agosto/Liquidacióncvs -agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4418" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86E9D54F-8F11-470A-9F0B-CFF8E1B24672}"/>
+  <xr:revisionPtr revIDLastSave="4442" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5665B1DD-F674-426C-931E-27F7E0906896}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -72630,7 +72630,7 @@
         <v>91</v>
       </c>
       <c r="G2775">
-        <v>0</v>
+        <v>44311744</v>
       </c>
     </row>
     <row r="2776" spans="1:8" x14ac:dyDescent="0.25">
@@ -73450,7 +73450,7 @@
         <v>91</v>
       </c>
       <c r="G2831">
-        <v>0</v>
+        <v>718800</v>
       </c>
     </row>
     <row r="2832" spans="1:7" x14ac:dyDescent="0.25">
@@ -73496,7 +73496,7 @@
         <v>91</v>
       </c>
       <c r="G2833">
-        <v>0</v>
+        <v>424000</v>
       </c>
     </row>
     <row r="2834" spans="1:7" x14ac:dyDescent="0.25">
@@ -73519,7 +73519,7 @@
         <v>91</v>
       </c>
       <c r="G2834">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="2835" spans="1:7" x14ac:dyDescent="0.25">
@@ -73565,7 +73565,7 @@
         <v>91</v>
       </c>
       <c r="G2836">
-        <v>0</v>
+        <v>1163900</v>
       </c>
     </row>
     <row r="2837" spans="1:7" x14ac:dyDescent="0.25">
@@ -73611,7 +73611,7 @@
         <v>91</v>
       </c>
       <c r="G2838">
-        <v>0</v>
+        <v>499000</v>
       </c>
     </row>
     <row r="2839" spans="1:7" x14ac:dyDescent="0.25">
@@ -73634,7 +73634,7 @@
         <v>91</v>
       </c>
       <c r="G2839">
-        <v>0</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="2840" spans="1:7" x14ac:dyDescent="0.25">
@@ -73657,7 +73657,7 @@
         <v>91</v>
       </c>
       <c r="G2840">
-        <v>0</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="2841" spans="1:7" x14ac:dyDescent="0.25">
@@ -73680,7 +73680,7 @@
         <v>91</v>
       </c>
       <c r="G2841">
-        <v>0</v>
+        <v>1962349</v>
       </c>
     </row>
     <row r="2842" spans="1:7" x14ac:dyDescent="0.25">
@@ -73703,7 +73703,7 @@
         <v>91</v>
       </c>
       <c r="G2842">
-        <v>0</v>
+        <v>1541000</v>
       </c>
     </row>
     <row r="2843" spans="1:7" x14ac:dyDescent="0.25">
@@ -73726,7 +73726,7 @@
         <v>91</v>
       </c>
       <c r="G2843">
-        <v>0</v>
+        <v>597000</v>
       </c>
     </row>
     <row r="2844" spans="1:7" x14ac:dyDescent="0.25">
@@ -73841,7 +73841,7 @@
         <v>91</v>
       </c>
       <c r="G2848">
-        <v>0</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="2849" spans="1:7" x14ac:dyDescent="0.25">
@@ -73864,7 +73864,7 @@
         <v>91</v>
       </c>
       <c r="G2849">
-        <v>0</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="2850" spans="1:7" x14ac:dyDescent="0.25">
@@ -73887,7 +73887,7 @@
         <v>91</v>
       </c>
       <c r="G2850">
-        <v>0</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="2851" spans="1:7" x14ac:dyDescent="0.25">
@@ -73910,7 +73910,7 @@
         <v>91</v>
       </c>
       <c r="G2851">
-        <v>0</v>
+        <v>1196000</v>
       </c>
     </row>
     <row r="2852" spans="1:7" x14ac:dyDescent="0.25">
@@ -73933,7 +73933,7 @@
         <v>91</v>
       </c>
       <c r="G2852">
-        <v>0</v>
+        <v>305000</v>
       </c>
     </row>
     <row r="2853" spans="1:7" x14ac:dyDescent="0.25">
@@ -73956,7 +73956,7 @@
         <v>91</v>
       </c>
       <c r="G2853">
-        <v>0</v>
+        <v>3299000</v>
       </c>
     </row>
     <row r="2854" spans="1:7" x14ac:dyDescent="0.25">
@@ -73979,7 +73979,7 @@
         <v>91</v>
       </c>
       <c r="G2854">
-        <v>0</v>
+        <v>341000</v>
       </c>
     </row>
     <row r="2855" spans="1:7" x14ac:dyDescent="0.25">
@@ -74002,7 +74002,7 @@
         <v>91</v>
       </c>
       <c r="G2855">
-        <v>0</v>
+        <v>806194.66</v>
       </c>
     </row>
     <row r="2856" spans="1:7" x14ac:dyDescent="0.25">
@@ -74025,7 +74025,7 @@
         <v>91</v>
       </c>
       <c r="G2856">
-        <v>0</v>
+        <v>2178000</v>
       </c>
     </row>
     <row r="2857" spans="1:7" x14ac:dyDescent="0.25">
@@ -74048,7 +74048,7 @@
         <v>91</v>
       </c>
       <c r="G2857">
-        <v>0</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="2858" spans="1:7" x14ac:dyDescent="0.25">
@@ -74094,7 +74094,7 @@
         <v>91</v>
       </c>
       <c r="G2859">
-        <v>0</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="2860" spans="1:7" x14ac:dyDescent="0.25">
@@ -74117,7 +74117,7 @@
         <v>91</v>
       </c>
       <c r="G2860">
-        <v>0</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="2861" spans="1:7" x14ac:dyDescent="0.25">
@@ -74140,7 +74140,7 @@
         <v>91</v>
       </c>
       <c r="G2861">
-        <v>0</v>
+        <v>1046000</v>
       </c>
     </row>
     <row r="2862" spans="1:7" x14ac:dyDescent="0.25">
@@ -74163,7 +74163,7 @@
         <v>91</v>
       </c>
       <c r="G2862">
-        <v>0</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="2863" spans="1:7" x14ac:dyDescent="0.25">
@@ -74186,7 +74186,7 @@
         <v>91</v>
       </c>
       <c r="G2863">
-        <v>0</v>
+        <v>355000</v>
       </c>
     </row>
     <row r="2864" spans="1:7" x14ac:dyDescent="0.25">
@@ -74209,7 +74209,7 @@
         <v>91</v>
       </c>
       <c r="G2864">
-        <v>0</v>
+        <v>2870000</v>
       </c>
     </row>
     <row r="2865" spans="1:7" x14ac:dyDescent="0.25">
@@ -74232,7 +74232,7 @@
         <v>91</v>
       </c>
       <c r="G2865">
-        <v>0</v>
+        <v>825000</v>
       </c>
     </row>
     <row r="2866" spans="1:7" x14ac:dyDescent="0.25">
@@ -74255,7 +74255,7 @@
         <v>91</v>
       </c>
       <c r="G2866">
-        <v>0</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="2867" spans="1:7" x14ac:dyDescent="0.25">
@@ -74278,7 +74278,7 @@
         <v>91</v>
       </c>
       <c r="G2867">
-        <v>0</v>
+        <v>2823900</v>
       </c>
     </row>
     <row r="2868" spans="1:7" x14ac:dyDescent="0.25">
@@ -74301,7 +74301,7 @@
         <v>91</v>
       </c>
       <c r="G2868">
-        <v>0</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="2869" spans="1:7" x14ac:dyDescent="0.25">
@@ -74324,7 +74324,7 @@
         <v>91</v>
       </c>
       <c r="G2869">
-        <v>0</v>
+        <v>370000</v>
       </c>
     </row>
     <row r="2870" spans="1:7" x14ac:dyDescent="0.25">
@@ -74347,7 +74347,7 @@
         <v>91</v>
       </c>
       <c r="G2870">
-        <v>0</v>
+        <v>651000</v>
       </c>
     </row>
     <row r="2871" spans="1:7" x14ac:dyDescent="0.25">
@@ -74370,7 +74370,7 @@
         <v>91</v>
       </c>
       <c r="G2871">
-        <v>0</v>
+        <v>1592000</v>
       </c>
     </row>
     <row r="2872" spans="1:7" x14ac:dyDescent="0.25">
@@ -74393,7 +74393,7 @@
         <v>91</v>
       </c>
       <c r="G2872">
-        <v>0</v>
+        <v>799000</v>
       </c>
     </row>
     <row r="2873" spans="1:7" x14ac:dyDescent="0.25">
@@ -74416,7 +74416,7 @@
         <v>91</v>
       </c>
       <c r="G2873">
-        <v>0</v>
+        <v>1891000</v>
       </c>
     </row>
     <row r="2874" spans="1:7" x14ac:dyDescent="0.25">
@@ -74439,7 +74439,7 @@
         <v>91</v>
       </c>
       <c r="G2874">
-        <v>0</v>
+        <v>1428900</v>
       </c>
     </row>
     <row r="2875" spans="1:7" x14ac:dyDescent="0.25">
@@ -74508,7 +74508,7 @@
         <v>91</v>
       </c>
       <c r="G2877">
-        <v>0</v>
+        <v>1238000</v>
       </c>
     </row>
     <row r="2878" spans="1:7" x14ac:dyDescent="0.25">
@@ -74531,7 +74531,7 @@
         <v>91</v>
       </c>
       <c r="G2878">
-        <v>0</v>
+        <v>638000</v>
       </c>
     </row>
     <row r="2879" spans="1:7" x14ac:dyDescent="0.25">
@@ -74554,7 +74554,7 @@
         <v>91</v>
       </c>
       <c r="G2879">
-        <v>0</v>
+        <v>1002000</v>
       </c>
     </row>
     <row r="2880" spans="1:7" x14ac:dyDescent="0.25">
@@ -74577,7 +74577,7 @@
         <v>91</v>
       </c>
       <c r="G2880">
-        <v>0</v>
+        <v>944000</v>
       </c>
     </row>
     <row r="2881" spans="1:7" x14ac:dyDescent="0.25">
